--- a/Assets/LingBoCanteen/Datatables/Excel/Sound.xlsx
+++ b/Assets/LingBoCanteen/Datatables/Excel/Sound.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game\GoldenDolphin\Assets\LingBoCanteen\1_Datatables\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\project\GoldenDolphin\GoldenDolphin\GoldenDolphinGame\Assets\LingBoCanteen\Datatables\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4378AE13-7C30-4D28-A159-9FAF8DB4B528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C90F15-9AF1-4DAE-B9E9-74ADF3F051C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>#</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,6 +61,115 @@
   <si>
     <t>音效编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>菜板切菜打击音效</t>
+  </si>
+  <si>
+    <t>cut_knife</t>
+  </si>
+  <si>
+    <t>榨汁机持续工作循环音</t>
+  </si>
+  <si>
+    <t>juicer_loop</t>
+  </si>
+  <si>
+    <t>灶台开火音效</t>
+  </si>
+  <si>
+    <t>stove_on</t>
+  </si>
+  <si>
+    <t>烹饪完成提示音</t>
+  </si>
+  <si>
+    <t>cook_complete</t>
+  </si>
+  <si>
+    <t>菜品烧糊失败音效</t>
+  </si>
+  <si>
+    <t>food_burn</t>
+  </si>
+  <si>
+    <t>顾客进店门铃音效</t>
+  </si>
+  <si>
+    <t>customer_enter</t>
+  </si>
+  <si>
+    <t>顾客满意离开结算音效</t>
+  </si>
+  <si>
+    <t>customer_leave</t>
+  </si>
+  <si>
+    <t>顾客生气超时离场音效</t>
+  </si>
+  <si>
+    <t>customer_angry</t>
+  </si>
+  <si>
+    <t>拖拽食材放置工作台音效</t>
+  </si>
+  <si>
+    <t>ingredient_place</t>
+  </si>
+  <si>
+    <t>完成订单获取金币音效</t>
+  </si>
+  <si>
+    <t>gold_get</t>
+  </si>
+  <si>
+    <t>SAN 数值上升音效</t>
+  </si>
+  <si>
+    <t>san_up</t>
+  </si>
+  <si>
+    <t>SAN 数值下降音效</t>
+  </si>
+  <si>
+    <t>san_down</t>
+  </si>
+  <si>
+    <t>人间 / 天堂 / 地狱区域切换过渡音</t>
+  </si>
+  <si>
+    <t>area_switch</t>
+  </si>
+  <si>
+    <t>select</t>
+  </si>
+  <si>
+    <t>选中 / 拾取食材音效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超市购买成功音效</t>
+  </si>
+  <si>
+    <t>buy_success</t>
+  </si>
+  <si>
+    <t>超市金币不足购买失败</t>
+  </si>
+  <si>
+    <t>buy_fail</t>
+  </si>
+  <si>
+    <t>配方 / 食材解锁提示音效</t>
+  </si>
+  <si>
+    <t>unlock</t>
+  </si>
+  <si>
+    <t>顾客耐心倒计时警告音</t>
+  </si>
+  <si>
+    <t>patience_warn</t>
   </si>
 </sst>
 </file>
@@ -91,10 +200,36 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -103,10 +238,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -388,15 +529,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.9296875" customWidth="1"/>
-    <col min="3" max="3" width="10.59765625" customWidth="1"/>
-    <col min="4" max="4" width="13.19921875" customWidth="1"/>
+    <col min="2" max="2" width="18.9140625" customWidth="1"/>
+    <col min="3" max="3" width="31.08203125" customWidth="1"/>
+    <col min="4" max="4" width="17.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -407,7 +548,7 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +561,7 @@
       </c>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -433,7 +574,7 @@
       </c>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -448,23 +589,208 @@
       </c>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="2">
+        <v>20000</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
-      <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="2">
+        <v>20001</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1"/>
+      <c r="B7" s="2">
+        <v>20002</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="2">
+        <v>20003</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="2">
+        <v>20004</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="2">
+        <v>20005</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="2">
+        <v>20006</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="2">
+        <v>20007</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="2">
+        <v>20008</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="2">
+        <v>20009</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="2">
+        <v>20010</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="2">
+        <v>20011</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="2">
+        <v>20012</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="3">
+        <v>20013</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="3">
+        <v>20014</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="3">
+        <v>20015</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="3">
+        <v>20016</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="3">
+        <v>20017</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/LingBoCanteen/Datatables/Excel/Sound.xlsx
+++ b/Assets/LingBoCanteen/Datatables/Excel/Sound.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\project\GoldenDolphin\GoldenDolphin\GoldenDolphinGame\Assets\LingBoCanteen\Datatables\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\project\GoldenDolphin\GoldenDolphin\GoldenDolphinGame\Assets\LingBoCanteen\DataTables\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C90F15-9AF1-4DAE-B9E9-74ADF3F051C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B01484B-4510-4550-85A2-471CBE39F6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -200,36 +200,10 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -238,16 +212,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -574,7 +545,7 @@
       </c>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -589,8 +560,7 @@
       </c>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1"/>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>20000</v>
       </c>
@@ -600,10 +570,8 @@
       <c r="D5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>20001</v>
       </c>
@@ -613,10 +581,8 @@
       <c r="D6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>20002</v>
       </c>
@@ -627,7 +593,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>20003</v>
       </c>
@@ -638,7 +604,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>20004</v>
       </c>
@@ -649,7 +615,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>20005</v>
       </c>
@@ -660,7 +626,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>20006</v>
       </c>
@@ -671,7 +637,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>20007</v>
       </c>
@@ -682,7 +648,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>20008</v>
       </c>
@@ -693,7 +659,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>20009</v>
       </c>
@@ -704,7 +670,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>20010</v>
       </c>
@@ -715,7 +681,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>20011</v>
       </c>
@@ -726,7 +692,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>20012</v>
       </c>
@@ -737,8 +703,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="3">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="2">
         <v>20013</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -748,8 +714,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="3">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="2">
         <v>20014</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -759,8 +725,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="3">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="2">
         <v>20015</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -770,8 +736,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="3">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" s="2">
         <v>20016</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -781,8 +747,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="3">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B22" s="2">
         <v>20017</v>
       </c>
       <c r="C22" s="2" t="s">
